--- a/excel/templates/initial-setup-template-v1（テスト株式会社）.xlsx
+++ b/excel/templates/initial-setup-template-v1（テスト株式会社）.xlsx
@@ -41,7 +41,7 @@
     <t>使用有無</t>
   </si>
   <si>
-    <t>経費タイプID</t>
+    <t>経費タイプコード</t>
   </si>
   <si>
     <t>経費タイプ名</t>
